--- a/data/trans_orig/P35A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023</t>
+          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42605</t>
+          <t>42301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63533</t>
+          <t>64327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70778</t>
+          <t>70985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161460</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200014</t>
+          <t>198483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>275411</t>
+          <t>274910</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>316810</t>
+          <t>315823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444780</t>
+          <t>443699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>500809</t>
+          <t>503777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269207</t>
+          <t>267898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>309388</t>
+          <t>310849</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360377</t>
+          <t>361571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>401935</t>
+          <t>404335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643081</t>
+          <t>641242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>701053</t>
+          <t>703674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131481</t>
+          <t>131076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>234037</t>
+          <t>231969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118731</t>
+          <t>117830</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191203</t>
+          <t>192584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>277462</t>
+          <t>288282</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>405396</t>
+          <t>407392</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39180</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80553</t>
+          <t>79023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45841</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82272</t>
+          <t>80533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95752</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152064</t>
+          <t>150726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491558</t>
+          <t>487728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1203526</t>
+          <t>1203359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320351</t>
+          <t>321529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490596</t>
+          <t>487222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>893390</t>
+          <t>901160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1742078</t>
+          <t>1808205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>917190</t>
+          <t>901375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1519248</t>
+          <t>1521493</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1497257</t>
+          <t>1496526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1749632</t>
+          <t>1746569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2391245</t>
+          <t>2330216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3152226</t>
+          <t>3141650</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66353</t>
+          <t>67663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126768</t>
+          <t>127223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169217</t>
+          <t>169923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124033</t>
+          <t>122406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159816</t>
+          <t>160598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257593</t>
+          <t>257961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317270</t>
+          <t>314642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429493</t>
+          <t>429592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477686</t>
+          <t>477437</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471012</t>
+          <t>470913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>510233</t>
+          <t>511783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>914000</t>
+          <t>916395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>976394</t>
+          <t>977925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>204338</t>
+          <t>203110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>299146</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191310</t>
+          <t>188430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>265520</t>
+          <t>261865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>422937</t>
+          <t>415192</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>544824</t>
+          <t>542020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>65062</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108736</t>
+          <t>109860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82130</t>
+          <t>78126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121536</t>
+          <t>118795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161144</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216620</t>
+          <t>211976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>819143</t>
+          <t>816569</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1565195</t>
+          <t>1546545</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>671589</t>
+          <t>702078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>939640</t>
+          <t>939523</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1643988</t>
+          <t>1661001</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2522652</t>
+          <t>2484673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1616211</t>
+          <t>1640818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2265102</t>
+          <t>2270936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2354788</t>
+          <t>2358771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2703564</t>
+          <t>2708223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4018826</t>
+          <t>4049882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4794947</t>
+          <t>4764160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>37293</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52018</t>
+          <t>56804</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64327</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>84443</t>
+          <t>94097</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70985</t>
+          <t>79728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100119</t>
+          <t>111172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33188</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38190</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48287</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179283</t>
+          <t>193121</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159284</t>
+          <t>171198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>198483</t>
+          <t>215538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>295393</t>
+          <t>317756</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>274910</t>
+          <t>296811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>315823</t>
+          <t>339238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>474676</t>
+          <t>510878</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>443699</t>
+          <t>476119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>503777</t>
+          <t>538605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>290146</t>
+          <t>333785</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267898</t>
+          <t>310447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310849</t>
+          <t>354824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>382021</t>
+          <t>417079</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361571</t>
+          <t>395355</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>404335</t>
+          <t>438950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>672167</t>
+          <t>750865</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>641242</t>
+          <t>720839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>703674</t>
+          <t>782287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>754538</t>
+          <t>821032</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>754538</t>
+          <t>821032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>754538</t>
+          <t>821032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1269476</t>
+          <t>1399562</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1269476</t>
+          <t>1399562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1269476</t>
+          <t>1399562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,69 +1294,69 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194265</t>
+          <t>225920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131076</t>
+          <t>194936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>231969</t>
+          <t>263206</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>191357</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>164707</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>220039</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
           <t>10,13%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>159665</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>117830</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>192584</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>415</t>
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>353930</t>
+          <t>417277</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>288282</t>
+          <t>377113</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>407392</t>
+          <t>461642</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60550</t>
+          <t>68941</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79023</t>
+          <t>87136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64809</t>
+          <t>73084</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80533</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>142025</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>122139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150726</t>
+          <t>167957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>694958</t>
+          <t>486355</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487728</t>
+          <t>445169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1203359</t>
+          <t>528596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>427651</t>
+          <t>479779</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321529</t>
+          <t>448850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>487222</t>
+          <t>517828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1122609</t>
+          <t>966134</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>901160</t>
+          <t>916719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1808205</t>
+          <t>1025361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1340554</t>
+          <t>1449350</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>901375</t>
+          <t>1399614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1521493</t>
+          <t>1497411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1585698</t>
+          <t>1427172</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1496526</t>
+          <t>1388761</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1746569</t>
+          <t>1469008</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2926252</t>
+          <t>2876523</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2330216</t>
+          <t>2811214</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3141650</t>
+          <t>2938991</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,22 +1863,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26693</t>
+          <t>28340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49819</t>
+          <t>53479</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67663</t>
+          <t>70523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1976,22 +1976,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36172</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>147191</t>
+          <t>165100</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>127223</t>
+          <t>141983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169923</t>
+          <t>189335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140503</t>
+          <t>161743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122406</t>
+          <t>144556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160598</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>287695</t>
+          <t>326843</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257961</t>
+          <t>296463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314642</t>
+          <t>356327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>454376</t>
+          <t>496783</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429592</t>
+          <t>469490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477437</t>
+          <t>520070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>491682</t>
+          <t>542225</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>470913</t>
+          <t>515916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>511783</t>
+          <t>560621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>946057</t>
+          <t>1039008</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>916395</t>
+          <t>1005293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>977925</t>
+          <t>1072428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>259003</t>
+          <t>297620</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203110</t>
+          <t>261308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>299146</t>
+          <t>333828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>229188</t>
+          <t>267232</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188430</t>
+          <t>238755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>261865</t>
+          <t>301040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>488192</t>
+          <t>564853</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>415192</t>
+          <t>523016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>542020</t>
+          <t>615978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65062</t>
+          <t>78620</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109860</t>
+          <t>120197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>114314</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>97899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118795</t>
+          <t>136126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>187064</t>
+          <t>212882</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>187238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>211976</t>
+          <t>241874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1021433</t>
+          <t>844576</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>816569</t>
+          <t>793615</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1546545</t>
+          <t>898736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>863548</t>
+          <t>959279</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>702078</t>
+          <t>914034</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>939523</t>
+          <t>1004565</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1884980</t>
+          <t>1803855</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1661001</t>
+          <t>1734973</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2484673</t>
+          <t>1876755</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2085076</t>
+          <t>2279919</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1640818</t>
+          <t>2214125</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2270936</t>
+          <t>2344065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2459401</t>
+          <t>2386477</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2358771</t>
+          <t>2328004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2708223</t>
+          <t>2431684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4544477</t>
+          <t>4666395</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4049882</t>
+          <t>4580539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4764160</t>
+          <t>4744266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3652824</t>
+          <t>3727302</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3652824</t>
+          <t>3727302</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3652824</t>
+          <t>3727302</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7104713</t>
+          <t>7247985</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7104713</t>
+          <t>7247985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7104713</t>
+          <t>7247985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
